--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391945.4395354969</v>
+        <v>391945</v>
       </c>
       <c r="R2" t="n">
-        <v>6341576.905338082</v>
+        <v>6341577</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391945.4395354969</v>
+        <v>391945</v>
       </c>
       <c r="R3" t="n">
-        <v>6341576.905338082</v>
+        <v>6341577</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -916,12 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391945.4395354969</v>
+        <v>391945</v>
       </c>
       <c r="R4" t="n">
-        <v>6341576.905338082</v>
+        <v>6341577</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +951,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,12 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>391945.4395354969</v>
+        <v>391945</v>
       </c>
       <c r="R5" t="n">
-        <v>6341576.905338082</v>
+        <v>6341577</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,19 +1057,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1158,12 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>391945.4395354969</v>
+        <v>391945</v>
       </c>
       <c r="R6" t="n">
-        <v>6341576.905338082</v>
+        <v>6341577</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,19 +1163,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983857</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74149952</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>74412394</v>
       </c>
       <c r="B4" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74768852</v>
       </c>
       <c r="B5" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74770790</v>
       </c>
       <c r="B6" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43724-2023 artfynd.xlsx
+++ b/artfynd/A 43724-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73983857</v>
+        <v>74770790</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Hypochoeris maculata. LEG: Karin Michelsen, Kerstin Johansson</t>
+          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Platanthera bifolia. LEG: Karin Michelsen, Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74149952</v>
+        <v>74768852</v>
       </c>
       <c r="B3" t="n">
-        <v>98589</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,19 +792,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Dactylorhiza maculata ssp. maculata. LEG: Karin Michelsen, Kerstin Johansson</t>
+          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Platanthera chlorantha. LEG: Karin Michelsen, Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,27 +887,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74412394</v>
+        <v>73983857</v>
       </c>
       <c r="B4" t="n">
-        <v>106294</v>
+        <v>109814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Fraxinus excelsior. LEG: Karin Michelsen, Kerstin Johansson</t>
+          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Hypochoeris maculata. LEG: Karin Michelsen, Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74768852</v>
+        <v>74412394</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>106812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Platanthera chlorantha. LEG: Karin Michelsen, Kerstin Johansson</t>
+          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Fraxinus excelsior. LEG: Karin Michelsen, Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74770790</v>
+        <v>74149952</v>
       </c>
       <c r="B6" t="n">
-        <v>98703</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,23 +1110,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Platanthera bifolia. LEG: Karin Michelsen, Kerstin Johansson</t>
+          <t>Smålands flora 2007: KOO: 5C9i 0032. SOM: Dactylorhiza maculata ssp. maculata. LEG: Karin Michelsen, Kerstin Johansson</t>
         </is>
       </c>
       <c r="AD6" t="b">
